--- a/public/uploads/invoice/ERS05071-Invoice2.xlsx
+++ b/public/uploads/invoice/ERS05071-Invoice2.xlsx
@@ -52,7 +52,7 @@
     <t>Lakeview Road Bridge</t>
   </si>
   <si>
-    <t>02/20/2026</t>
+    <t>02/24/2026</t>
   </si>
   <si>
     <t>1258 Willingham Dr</t>
@@ -205,16 +205,13 @@
     <t>CLASS B CONC, BASE OR PVMT WIDENING</t>
   </si>
   <si>
-    <t>CONC CURB &amp; GUTTER 8 IN X 30 IN TP 2</t>
-  </si>
-  <si>
-    <t>BOND</t>
-  </si>
-  <si>
     <t>CONC CATCH BASIN TOP &amp; THROAT</t>
   </si>
   <si>
     <t>CONC DROP INLET</t>
+  </si>
+  <si>
+    <t>CONC CURB &amp; GUTTER 8 IN X 30 IN TP 2</t>
   </si>
   <si>
     <t>4 IN SIDEWALK $5 LOT</t>
@@ -238,6 +235,9 @@
     <t>ADJUST WATER VALVE TO GRADE</t>
   </si>
   <si>
+    <t>BOND</t>
+  </si>
+  <si>
     <t>CHANGE ORDER IN OCTOBER 2025</t>
   </si>
   <si>
@@ -250,16 +250,16 @@
     <t>CY</t>
   </si>
   <si>
+    <t>EA</t>
+  </si>
+  <si>
     <t>LF</t>
   </si>
   <si>
-    <t>LS</t>
+    <t>SF</t>
   </si>
   <si>
-    <t>EA</t>
-  </si>
-  <si>
-    <t>SF</t>
+    <t>LS</t>
   </si>
 </sst>
 </file>
@@ -1295,22 +1295,22 @@
     <xf xfId="0" fontId="1" numFmtId="2" fillId="0" borderId="0" applyFont="1" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" shrinkToFit="false"/>
     </xf>
-    <xf xfId="0" fontId="7" numFmtId="0" fillId="0" borderId="32" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
+    <xf xfId="0" fontId="1" numFmtId="0" fillId="0" borderId="32" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" shrinkToFit="false"/>
     </xf>
-    <xf xfId="0" fontId="7" numFmtId="0" fillId="11" borderId="32" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf xfId="0" fontId="1" numFmtId="0" fillId="11" borderId="32" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" shrinkToFit="false"/>
     </xf>
-    <xf xfId="0" fontId="7" numFmtId="0" fillId="11" borderId="32" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf xfId="0" fontId="1" numFmtId="0" fillId="11" borderId="32" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" shrinkToFit="false"/>
     </xf>
-    <xf xfId="0" fontId="7" numFmtId="164" fillId="11" borderId="32" applyFont="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf xfId="0" fontId="1" numFmtId="164" fillId="11" borderId="32" applyFont="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="true" shrinkToFit="false"/>
     </xf>
-    <xf xfId="0" fontId="7" numFmtId="4" fillId="11" borderId="32" applyFont="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf xfId="0" fontId="1" numFmtId="4" fillId="11" borderId="32" applyFont="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="true" shrinkToFit="false"/>
     </xf>
-    <xf xfId="0" fontId="7" numFmtId="4" fillId="0" borderId="32" applyFont="1" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1">
+    <xf xfId="0" fontId="1" numFmtId="4" fillId="0" borderId="32" applyFont="1" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
     </xf>
     <xf xfId="0" fontId="6" numFmtId="0" fillId="0" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="1">
@@ -2332,10 +2332,10 @@
         <v>58.0</v>
       </c>
       <c r="G17" s="119">
-        <v>1500.0</v>
+        <v>1.0</v>
       </c>
       <c r="H17" s="118">
-        <v>87000.0</v>
+        <v>58.0</v>
       </c>
       <c r="I17" s="119">
         <v>1266.50999999999999</v>
@@ -2457,44 +2457,44 @@
         <v>77</v>
       </c>
       <c r="F19" s="118">
-        <v>36.0</v>
+        <v>2200.0</v>
       </c>
       <c r="G19" s="119">
-        <v>2810.0</v>
+        <v>17.0</v>
       </c>
       <c r="H19" s="118">
-        <v>101160.0</v>
+        <v>37400.0</v>
       </c>
       <c r="I19" s="119">
-        <v>2572.0</v>
+        <v>35.5</v>
       </c>
       <c r="J19" s="118">
-        <v>92592.0</v>
+        <v>78100.0</v>
       </c>
       <c r="K19" s="119">
-        <v>2506.0</v>
+        <v>35.5</v>
       </c>
       <c r="L19" s="118">
-        <v>90216.0</v>
+        <v>78100.0</v>
       </c>
       <c r="M19" s="119">
-        <v>2506.0</v>
+        <v>35.5</v>
       </c>
       <c r="N19" s="118">
-        <v>90216.0</v>
+        <v>78100.0</v>
       </c>
       <c r="O19" s="119">
-        <v>66.0</v>
+        <v>0.0</v>
       </c>
       <c r="P19" s="118">
-        <v>2376.0</v>
+        <v>0.0</v>
       </c>
       <c r="Q19" s="120"/>
       <c r="R19" s="119">
-        <v>66.0</v>
+        <v>0.0</v>
       </c>
       <c r="S19" s="118">
-        <v>2376.0</v>
+        <v>0.0</v>
       </c>
       <c r="T19" s="1"/>
       <c r="U19" s="57"/>
@@ -2518,47 +2518,47 @@
       <c r="C20" s="115"/>
       <c r="D20" s="115"/>
       <c r="E20" s="117" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="F20" s="118">
-        <v>-1823.75</v>
+        <v>800.0</v>
       </c>
       <c r="G20" s="119">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="H20" s="118">
-        <v>-1823.75</v>
+        <v>1600.0</v>
       </c>
       <c r="I20" s="119">
-        <v>1.0</v>
+        <v>22.0</v>
       </c>
       <c r="J20" s="118">
-        <v>-1823.75</v>
+        <v>17600.0</v>
       </c>
       <c r="K20" s="119">
-        <v>0.950977</v>
+        <v>22.0</v>
       </c>
       <c r="L20" s="118">
-        <v>-1734.33999999999992</v>
+        <v>17600.0</v>
       </c>
       <c r="M20" s="119">
-        <v>0</v>
+        <v>22.0</v>
       </c>
       <c r="N20" s="118">
-        <v>0</v>
+        <v>17600.0</v>
       </c>
       <c r="O20" s="119">
-        <v>0.049023</v>
+        <v>0.0</v>
       </c>
       <c r="P20" s="118">
-        <v>-89.41</v>
+        <v>0.0</v>
       </c>
       <c r="Q20" s="120"/>
       <c r="R20" s="119">
-        <v>0.049023</v>
+        <v>0.0</v>
       </c>
       <c r="S20" s="118">
-        <v>-89.41</v>
+        <v>0.0</v>
       </c>
       <c r="T20" s="1"/>
       <c r="U20" s="57"/>
@@ -2582,47 +2582,47 @@
       <c r="C21" s="115"/>
       <c r="D21" s="115"/>
       <c r="E21" s="117" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="F21" s="118">
-        <v>2200.0</v>
+        <v>36.0</v>
       </c>
       <c r="G21" s="119">
-        <v>17.0</v>
+        <v>2810.0</v>
       </c>
       <c r="H21" s="118">
-        <v>37400.0</v>
+        <v>101160.0</v>
       </c>
       <c r="I21" s="119">
-        <v>0</v>
+        <v>2572.0</v>
       </c>
       <c r="J21" s="118">
-        <v>0</v>
+        <v>92592.0</v>
       </c>
       <c r="K21" s="119">
-        <v>0</v>
+        <v>2506.0</v>
       </c>
       <c r="L21" s="118">
-        <v>0</v>
+        <v>90216.0</v>
       </c>
       <c r="M21" s="119">
-        <v>0</v>
+        <v>2506.0</v>
       </c>
       <c r="N21" s="118">
-        <v>0</v>
+        <v>90216.0</v>
       </c>
       <c r="O21" s="119">
-        <v>0</v>
+        <v>66.0</v>
       </c>
       <c r="P21" s="118">
-        <v>0</v>
+        <v>2376.0</v>
       </c>
       <c r="Q21" s="120"/>
       <c r="R21" s="119">
-        <v>0</v>
+        <v>66.0</v>
       </c>
       <c r="S21" s="118">
-        <v>0</v>
+        <v>2376.0</v>
       </c>
       <c r="T21" s="1"/>
       <c r="U21" s="57"/>
@@ -2646,47 +2646,47 @@
       <c r="C22" s="115"/>
       <c r="D22" s="115"/>
       <c r="E22" s="117" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="F22" s="118">
-        <v>800.0</v>
+        <v>10.0</v>
       </c>
       <c r="G22" s="119">
-        <v>2.0</v>
+        <v>150.0</v>
       </c>
       <c r="H22" s="118">
-        <v>1600.0</v>
+        <v>1500.0</v>
       </c>
       <c r="I22" s="119">
-        <v>0</v>
+        <v>0.0</v>
       </c>
       <c r="J22" s="118">
-        <v>0</v>
+        <v>0.0</v>
       </c>
       <c r="K22" s="119">
-        <v>0</v>
+        <v>0.0</v>
       </c>
       <c r="L22" s="118">
-        <v>0</v>
+        <v>0.0</v>
       </c>
       <c r="M22" s="119">
-        <v>0</v>
+        <v>0.0</v>
       </c>
       <c r="N22" s="118">
-        <v>0</v>
+        <v>0.0</v>
       </c>
       <c r="O22" s="119">
-        <v>0</v>
+        <v>0.0</v>
       </c>
       <c r="P22" s="118">
-        <v>0</v>
+        <v>0.0</v>
       </c>
       <c r="Q22" s="120"/>
       <c r="R22" s="119">
-        <v>0</v>
+        <v>0.0</v>
       </c>
       <c r="S22" s="118">
-        <v>0</v>
+        <v>0.0</v>
       </c>
       <c r="T22" s="1"/>
       <c r="U22" s="57"/>
@@ -2710,47 +2710,47 @@
       <c r="C23" s="115"/>
       <c r="D23" s="115"/>
       <c r="E23" s="117" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="F23" s="118">
         <v>10.0</v>
       </c>
       <c r="G23" s="119">
-        <v>150.0</v>
+        <v>120.0</v>
       </c>
       <c r="H23" s="118">
-        <v>1500.0</v>
+        <v>1200.0</v>
       </c>
       <c r="I23" s="119">
-        <v>0</v>
+        <v>0.0</v>
       </c>
       <c r="J23" s="118">
-        <v>0</v>
+        <v>0.0</v>
       </c>
       <c r="K23" s="119">
-        <v>0</v>
+        <v>0.0</v>
       </c>
       <c r="L23" s="118">
-        <v>0</v>
+        <v>0.0</v>
       </c>
       <c r="M23" s="119">
-        <v>0</v>
+        <v>0.0</v>
       </c>
       <c r="N23" s="118">
-        <v>0</v>
+        <v>0.0</v>
       </c>
       <c r="O23" s="119">
-        <v>0</v>
+        <v>0.0</v>
       </c>
       <c r="P23" s="118">
-        <v>0</v>
+        <v>0.0</v>
       </c>
       <c r="Q23" s="120"/>
       <c r="R23" s="119">
-        <v>0</v>
+        <v>0.0</v>
       </c>
       <c r="S23" s="118">
-        <v>0</v>
+        <v>0.0</v>
       </c>
       <c r="T23" s="1"/>
       <c r="U23" s="57"/>
@@ -2774,47 +2774,47 @@
       <c r="C24" s="115"/>
       <c r="D24" s="115"/>
       <c r="E24" s="117" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="F24" s="118">
         <v>10.0</v>
       </c>
       <c r="G24" s="119">
-        <v>120.0</v>
+        <v>500.0</v>
       </c>
       <c r="H24" s="118">
-        <v>1200.0</v>
+        <v>5000.0</v>
       </c>
       <c r="I24" s="119">
-        <v>0</v>
+        <v>0.0</v>
       </c>
       <c r="J24" s="118">
-        <v>0</v>
+        <v>0.0</v>
       </c>
       <c r="K24" s="119">
-        <v>0</v>
+        <v>0.0</v>
       </c>
       <c r="L24" s="118">
-        <v>0</v>
+        <v>0.0</v>
       </c>
       <c r="M24" s="119">
-        <v>0</v>
+        <v>0.0</v>
       </c>
       <c r="N24" s="118">
-        <v>0</v>
+        <v>0.0</v>
       </c>
       <c r="O24" s="119">
-        <v>0</v>
+        <v>0.0</v>
       </c>
       <c r="P24" s="118">
-        <v>0</v>
+        <v>0.0</v>
       </c>
       <c r="Q24" s="120"/>
       <c r="R24" s="119">
-        <v>0</v>
+        <v>0.0</v>
       </c>
       <c r="S24" s="118">
-        <v>0</v>
+        <v>0.0</v>
       </c>
       <c r="T24" s="1"/>
       <c r="U24" s="57"/>
@@ -2838,47 +2838,47 @@
       <c r="C25" s="115"/>
       <c r="D25" s="115"/>
       <c r="E25" s="117" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="F25" s="118">
-        <v>10.0</v>
+        <v>20.0</v>
       </c>
       <c r="G25" s="119">
         <v>500.0</v>
       </c>
       <c r="H25" s="118">
-        <v>5000.0</v>
+        <v>10000.0</v>
       </c>
       <c r="I25" s="119">
-        <v>0</v>
+        <v>50.0</v>
       </c>
       <c r="J25" s="118">
-        <v>0</v>
+        <v>1000.0</v>
       </c>
       <c r="K25" s="119">
-        <v>0</v>
+        <v>50.0</v>
       </c>
       <c r="L25" s="118">
-        <v>0</v>
+        <v>1000.0</v>
       </c>
       <c r="M25" s="119">
-        <v>0</v>
+        <v>50.0</v>
       </c>
       <c r="N25" s="118">
-        <v>0</v>
+        <v>1000.0</v>
       </c>
       <c r="O25" s="119">
-        <v>0</v>
+        <v>0.0</v>
       </c>
       <c r="P25" s="118">
-        <v>0</v>
+        <v>0.0</v>
       </c>
       <c r="Q25" s="120"/>
       <c r="R25" s="119">
-        <v>0</v>
+        <v>0.0</v>
       </c>
       <c r="S25" s="118">
-        <v>0</v>
+        <v>0.0</v>
       </c>
       <c r="T25" s="1"/>
       <c r="U25" s="57"/>
@@ -2902,47 +2902,47 @@
       <c r="C26" s="115"/>
       <c r="D26" s="115"/>
       <c r="E26" s="117" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="F26" s="118">
         <v>20.0</v>
       </c>
       <c r="G26" s="119">
-        <v>500.0</v>
+        <v>523.0</v>
       </c>
       <c r="H26" s="118">
-        <v>10000.0</v>
+        <v>10460.0</v>
       </c>
       <c r="I26" s="119">
-        <v>0</v>
+        <v>12.0</v>
       </c>
       <c r="J26" s="118">
-        <v>0</v>
+        <v>240.0</v>
       </c>
       <c r="K26" s="119">
-        <v>0</v>
+        <v>12.0</v>
       </c>
       <c r="L26" s="118">
-        <v>0</v>
+        <v>240.0</v>
       </c>
       <c r="M26" s="119">
-        <v>0</v>
+        <v>12.0</v>
       </c>
       <c r="N26" s="118">
-        <v>0</v>
+        <v>240.0</v>
       </c>
       <c r="O26" s="119">
-        <v>0</v>
+        <v>0.0</v>
       </c>
       <c r="P26" s="118">
-        <v>0</v>
+        <v>0.0</v>
       </c>
       <c r="Q26" s="120"/>
       <c r="R26" s="119">
-        <v>0</v>
+        <v>0.0</v>
       </c>
       <c r="S26" s="118">
-        <v>0</v>
+        <v>0.0</v>
       </c>
       <c r="T26" s="1"/>
       <c r="U26" s="57"/>
@@ -2966,47 +2966,47 @@
       <c r="C27" s="115"/>
       <c r="D27" s="115"/>
       <c r="E27" s="117" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="F27" s="118">
-        <v>20.0</v>
+        <v>12.0</v>
       </c>
       <c r="G27" s="119">
-        <v>523.0</v>
+        <v>250.0</v>
       </c>
       <c r="H27" s="118">
-        <v>10460.0</v>
+        <v>3000.0</v>
       </c>
       <c r="I27" s="119">
-        <v>0</v>
+        <v>0.0</v>
       </c>
       <c r="J27" s="118">
-        <v>0</v>
+        <v>0.0</v>
       </c>
       <c r="K27" s="119">
-        <v>0</v>
+        <v>0.0</v>
       </c>
       <c r="L27" s="118">
-        <v>0</v>
+        <v>0.0</v>
       </c>
       <c r="M27" s="119">
-        <v>0</v>
+        <v>0.0</v>
       </c>
       <c r="N27" s="118">
-        <v>0</v>
+        <v>0.0</v>
       </c>
       <c r="O27" s="119">
-        <v>0</v>
+        <v>0.0</v>
       </c>
       <c r="P27" s="118">
-        <v>0</v>
+        <v>0.0</v>
       </c>
       <c r="Q27" s="120"/>
       <c r="R27" s="119">
-        <v>0</v>
+        <v>0.0</v>
       </c>
       <c r="S27" s="118">
-        <v>0</v>
+        <v>0.0</v>
       </c>
       <c r="T27" s="1"/>
       <c r="U27" s="57"/>
@@ -3030,47 +3030,47 @@
       <c r="C28" s="115"/>
       <c r="D28" s="115"/>
       <c r="E28" s="117" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="F28" s="118">
-        <v>12.0</v>
+        <v>10.0</v>
       </c>
       <c r="G28" s="119">
-        <v>250.0</v>
+        <v>125.0</v>
       </c>
       <c r="H28" s="118">
-        <v>3000.0</v>
+        <v>1250.0</v>
       </c>
       <c r="I28" s="119">
-        <v>0</v>
+        <v>32.0</v>
       </c>
       <c r="J28" s="118">
-        <v>0</v>
+        <v>320.0</v>
       </c>
       <c r="K28" s="119">
-        <v>0</v>
+        <v>32.0</v>
       </c>
       <c r="L28" s="118">
-        <v>0</v>
+        <v>320.0</v>
       </c>
       <c r="M28" s="119">
-        <v>0</v>
+        <v>32.0</v>
       </c>
       <c r="N28" s="118">
-        <v>0</v>
+        <v>320.0</v>
       </c>
       <c r="O28" s="119">
-        <v>0</v>
+        <v>0.0</v>
       </c>
       <c r="P28" s="118">
-        <v>0</v>
+        <v>0.0</v>
       </c>
       <c r="Q28" s="120"/>
       <c r="R28" s="119">
-        <v>0</v>
+        <v>0.0</v>
       </c>
       <c r="S28" s="118">
-        <v>0</v>
+        <v>0.0</v>
       </c>
       <c r="T28" s="1"/>
       <c r="U28" s="57"/>
@@ -3094,28 +3094,28 @@
       <c r="C29" s="115"/>
       <c r="D29" s="115"/>
       <c r="E29" s="117" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F29" s="118">
-        <v>10.0</v>
+        <v>-1823.75</v>
       </c>
       <c r="G29" s="119">
-        <v>125.0</v>
+        <v>1.0</v>
       </c>
       <c r="H29" s="118">
-        <v>1250.0</v>
+        <v>-1823.75</v>
       </c>
       <c r="I29" s="119">
-        <v>0</v>
+        <v>1.0</v>
       </c>
       <c r="J29" s="118">
-        <v>0</v>
+        <v>-1823.75</v>
       </c>
       <c r="K29" s="119">
-        <v>0</v>
+        <v>1.0</v>
       </c>
       <c r="L29" s="118">
-        <v>0</v>
+        <v>-1823.75</v>
       </c>
       <c r="M29" s="119">
         <v>0</v>
@@ -3124,17 +3124,17 @@
         <v>0</v>
       </c>
       <c r="O29" s="119">
-        <v>0</v>
+        <v>0.0</v>
       </c>
       <c r="P29" s="118">
-        <v>0</v>
+        <v>0.0</v>
       </c>
       <c r="Q29" s="120"/>
       <c r="R29" s="119">
-        <v>0</v>
+        <v>0.0</v>
       </c>
       <c r="S29" s="118">
-        <v>0</v>
+        <v>0.0</v>
       </c>
       <c r="T29" s="1"/>
       <c r="U29" s="57"/>
@@ -3290,35 +3290,35 @@
       </c>
       <c r="H33" s="92">
         <f>SUM(H16:H32)</f>
-        <v>268718.25</v>
+        <v>181776.25</v>
       </c>
       <c r="I33" s="93" t="s">
         <v>57</v>
       </c>
       <c r="J33" s="94">
         <f>SUM(J16:J32)</f>
-        <v>203597.019999999989523</v>
+        <v>300857.020000000018626</v>
       </c>
       <c r="K33" s="95" t="s">
         <v>56</v>
       </c>
       <c r="L33" s="96">
         <f>SUM(L16:L32)</f>
-        <v>161911.20000000001164</v>
+        <v>259081.79000000000815</v>
       </c>
       <c r="M33" s="97" t="s">
         <v>55</v>
       </c>
       <c r="N33" s="98">
         <f>SUM(N16:N32)</f>
-        <v>163645.54000000000815</v>
+        <v>260905.54000000000815</v>
       </c>
       <c r="O33" s="99" t="s">
         <v>54</v>
       </c>
       <c r="P33" s="100">
         <f>SUM(P16:P32)</f>
-        <v>41685.81999999999971</v>
+        <v>41775.2300000000032</v>
       </c>
       <c r="Q33" s="8"/>
       <c r="R33" s="101" t="s">
@@ -3326,7 +3326,7 @@
       </c>
       <c r="S33" s="102">
         <f>SUM(S16:S32)</f>
-        <v>41685.81999999999971</v>
+        <v>41775.2300000000032</v>
       </c>
       <c r="T33" s="1"/>
       <c r="U33" s="57"/>
@@ -3389,7 +3389,7 @@
       </c>
       <c r="J35" s="134">
         <f>J33-J34</f>
-        <v>203597.019999999989523</v>
+        <v>300857.020000000018626</v>
       </c>
       <c r="K35" s="106"/>
       <c r="L35" s="108"/>
@@ -3403,7 +3403,7 @@
       </c>
       <c r="S35" s="136">
         <f>S33-S34</f>
-        <v>41685.81999999999971</v>
+        <v>41775.2300000000032</v>
       </c>
       <c r="T35" s="1"/>
       <c r="U35" s="110"/>
